--- a/templates/2027/mock/02_組織架構及聯絡.xlsx
+++ b/templates/2027/mock/02_組織架構及聯絡.xlsx
@@ -51,7 +51,10 @@
           <t xml:space="preserve">盡量 — 填得幾多得幾多
 型別：text
 例：黃偉安
-空缺就留空，備註寫「待定」</t>
+空缺就留空，備註寫「待定」
+一格只准一個人。兩個人要開兩行 —— 2026 就係有一格寫咗兩個人，搞到 55 行變 54 人。
+✓ 可以：陳大文、區永樑先生
+✗ 唔好：陳大文、李小明、陳大文/李小明、陳大文 (待定)</t>
         </r>
       </text>
     </comment>
@@ -61,7 +64,10 @@
           <t xml:space="preserve">盡量 — 填得幾多得幾多
 型別：phone
 例：92157472
-8 位數字。錯咗就登入唔到 APP</t>
+8 位數字。錯咗就登入唔到 APP
+只准填 8 位數字。唔好加 +852、空格、斜線或者「／」。
+✓ 可以：92157472
+✗ 唔好：+852 9215 7472、9215 7472、92157472/98765432（兩個號碼）、待定</t>
         </r>
       </text>
     </comment>
@@ -1002,7 +1008,7 @@
     <t>級別</t>
   </si>
   <si>
-    <t>型別</t>
+    <t>格式</t>
   </si>
   <si>
     <t>例子</t>
@@ -1029,16 +1035,16 @@
     <t>D</t>
   </si>
   <si>
-    <t>空缺就留空，備註寫「待定」</t>
+    <t>陳大文</t>
+  </si>
+  <si>
+    <t>一格只准一個人。兩個人要開兩行 —— 2026 就係有一格寫咗兩個人，搞到 55 行變 54 人。　✓陳大文／區永樑先生　✗陳大文、李小明／陳大文/李小明／陳大文 (待定)　空缺就留空，備註寫「待定」</t>
   </si>
   <si>
     <t>E</t>
   </si>
   <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>8 位數字。錯咗就登入唔到 APP</t>
+    <t>只准填 8 位數字。唔好加 +852、空格、斜線或者「／」。　✓92157472　✗+852 9215 7472／9215 7472／92157472/98765432（兩個號碼）／待定　8 位數字。錯咗就登入唔到 APP</t>
   </si>
   <si>
     <t>F</t>
@@ -1492,7 +1498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H580"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="6" width="10.8" customWidth="1"/>
@@ -1552,2088 +1558,2592 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="347" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="348" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="349" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="360" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="361" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="373" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="374" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="375" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="376" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="377" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="379" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="380" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="386" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="387" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="388" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="389" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="390" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="391" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="392" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="393" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="394" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="395" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="396" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="397" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="399" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="401" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="402" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="403" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="404" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="405" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="406" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="407" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="408" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="409" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="410" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="411" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="412" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="413" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="414" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="415" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="416" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="417" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="418" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="419" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="420" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="421" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="422" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="424" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="425" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="426" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="427" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="428" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="429" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="430" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="431" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="432" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="433" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="434" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="435" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="436" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="437" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="438" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="439" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="440" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="441" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="442" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="443" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="444" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="445" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="446" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="447" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="448" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="449" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="450" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="451" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="452" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="453" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="454" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="455" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="456" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="457" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="458" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="459" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="460" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="461" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="462" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="463" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="464" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="465" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="466" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="467" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="468" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="469" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="470" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="471" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="472" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="473" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="474" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="475" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="476" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="477" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="478" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="479" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="480" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="497" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="498" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="499" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="500" spans="4:5" x14ac:dyDescent="0.25"/>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B501" t="s">
+        <v>11</v>
+      </c>
+      <c r="C501" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D501" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E501" t="s">
         <v>14</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F501" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G501" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="H501" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B502" t="s">
+        <v>11</v>
+      </c>
+      <c r="C502" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D502" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E502" t="s">
         <v>18</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F502" t="s">
         <v>19</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G502" t="s">
         <v>16</v>
       </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="H502" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B503" t="s">
+        <v>11</v>
+      </c>
+      <c r="C503" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D503" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E503" t="s">
         <v>23</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F503" t="s">
         <v>24</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G503" t="s">
         <v>25</v>
       </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="H503" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B504" t="s">
+        <v>11</v>
+      </c>
+      <c r="C504" t="s">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D504" t="s">
         <v>27</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E504" t="s">
         <v>28</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F504" t="s">
         <v>29</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G504" t="s">
         <v>30</v>
       </c>
-      <c r="H6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="H504" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
         <v>31</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B505" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C505" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D505" t="s">
         <v>34</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E505" t="s">
         <v>35</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F505" t="s">
         <v>36</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G505" t="s">
         <v>37</v>
       </c>
-      <c r="H7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="H505" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
         <v>31</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B506" t="s">
         <v>38</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C506" t="s">
         <v>39</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D506" t="s">
         <v>40</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E506" t="s">
         <v>41</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F506" t="s">
         <v>42</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G506" t="s">
         <v>43</v>
       </c>
-      <c r="H8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="H506" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
         <v>31</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B507" t="s">
         <v>38</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C507" t="s">
         <v>44</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D507" t="s">
         <v>45</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E507" t="s">
         <v>46</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F507" t="s">
         <v>47</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G507" t="s">
         <v>48</v>
       </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="H507" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
         <v>31</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B508" t="s">
         <v>49</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C508" t="s">
         <v>50</v>
       </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="D508" t="s">
+        <v>11</v>
+      </c>
+      <c r="E508" t="s">
+        <v>11</v>
+      </c>
+      <c r="F508" t="s">
+        <v>11</v>
+      </c>
+      <c r="G508" t="s">
+        <v>11</v>
+      </c>
+      <c r="H508" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
         <v>31</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B509" t="s">
         <v>49</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C509" t="s">
         <v>50</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="D509" t="s">
+        <v>11</v>
+      </c>
+      <c r="E509" t="s">
+        <v>11</v>
+      </c>
+      <c r="F509" t="s">
+        <v>11</v>
+      </c>
+      <c r="G509" t="s">
+        <v>11</v>
+      </c>
+      <c r="H509" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
         <v>31</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B510" t="s">
         <v>49</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C510" t="s">
         <v>51</v>
       </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="D510" t="s">
+        <v>11</v>
+      </c>
+      <c r="E510" t="s">
+        <v>11</v>
+      </c>
+      <c r="F510" t="s">
+        <v>11</v>
+      </c>
+      <c r="G510" t="s">
+        <v>11</v>
+      </c>
+      <c r="H510" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
         <v>31</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B511" t="s">
         <v>49</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C511" t="s">
         <v>52</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D511" t="s">
         <v>53</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E511" t="s">
         <v>54</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F511" t="s">
         <v>55</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G511" t="s">
         <v>37</v>
       </c>
-      <c r="H13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="H511" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
         <v>31</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B512" t="s">
         <v>49</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C512" t="s">
         <v>56</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D512" t="s">
         <v>57</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E512" t="s">
         <v>58</v>
       </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="F512" t="s">
+        <v>11</v>
+      </c>
+      <c r="G512" t="s">
         <v>59</v>
       </c>
-      <c r="H14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="H512" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
         <v>31</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B513" t="s">
         <v>49</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C513" t="s">
         <v>60</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D513" t="s">
         <v>61</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E513" t="s">
         <v>62</v>
       </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="F513" t="s">
+        <v>11</v>
+      </c>
+      <c r="G513" t="s">
         <v>37</v>
       </c>
-      <c r="H15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="H513" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
         <v>31</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B514" t="s">
         <v>49</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C514" t="s">
         <v>63</v>
       </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="D514" t="s">
+        <v>11</v>
+      </c>
+      <c r="E514" t="s">
+        <v>11</v>
+      </c>
+      <c r="F514" t="s">
+        <v>11</v>
+      </c>
+      <c r="G514" t="s">
+        <v>11</v>
+      </c>
+      <c r="H514" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
         <v>31</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B515" t="s">
         <v>49</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C515" t="s">
         <v>64</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D515" t="s">
         <v>65</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E515" t="s">
         <v>66</v>
       </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="F515" t="s">
+        <v>11</v>
+      </c>
+      <c r="G515" t="s">
         <v>67</v>
       </c>
-      <c r="H17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="H515" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
         <v>68</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B516" t="s">
         <v>32</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C516" t="s">
         <v>69</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D516" t="s">
         <v>70</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E516" t="s">
         <v>71</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F516" t="s">
         <v>72</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G516" t="s">
         <v>73</v>
       </c>
-      <c r="H18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="H516" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
         <v>68</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B517" t="s">
         <v>38</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C517" t="s">
         <v>74</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D517" t="s">
         <v>75</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E517" t="s">
         <v>76</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F517" t="s">
         <v>77</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G517" t="s">
         <v>73</v>
       </c>
-      <c r="H19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="H517" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
         <v>68</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B518" t="s">
         <v>49</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C518" t="s">
         <v>78</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D518" t="s">
         <v>79</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E518" t="s">
         <v>80</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F518" t="s">
         <v>81</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G518" t="s">
         <v>73</v>
       </c>
-      <c r="H20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="H518" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
         <v>68</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B519" t="s">
         <v>49</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C519" t="s">
         <v>82</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D519" t="s">
         <v>83</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E519" t="s">
         <v>84</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F519" t="s">
         <v>85</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G519" t="s">
         <v>73</v>
       </c>
-      <c r="H21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="H519" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
         <v>68</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B520" t="s">
         <v>49</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C520" t="s">
         <v>86</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D520" t="s">
         <v>87</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E520" t="s">
         <v>88</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F520" t="s">
         <v>89</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G520" t="s">
         <v>73</v>
       </c>
-      <c r="H22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="H520" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
         <v>68</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B521" t="s">
         <v>49</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C521" t="s">
         <v>90</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D521" t="s">
         <v>91</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E521" t="s">
         <v>92</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F521" t="s">
         <v>93</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G521" t="s">
         <v>73</v>
       </c>
-      <c r="H23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="H521" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
         <v>68</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B522" t="s">
         <v>49</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C522" t="s">
         <v>94</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D522" t="s">
         <v>95</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E522" t="s">
         <v>96</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F522" t="s">
         <v>97</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G522" t="s">
         <v>73</v>
       </c>
-      <c r="H24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="H522" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
         <v>98</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B523" t="s">
         <v>32</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C523" t="s">
         <v>99</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D523" t="s">
         <v>100</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E523" t="s">
         <v>101</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F523" t="s">
         <v>102</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G523" t="s">
         <v>103</v>
       </c>
-      <c r="H25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="H523" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
         <v>98</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B524" t="s">
         <v>38</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C524" t="s">
         <v>104</v>
       </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="D524" t="s">
+        <v>11</v>
+      </c>
+      <c r="E524" t="s">
+        <v>11</v>
+      </c>
+      <c r="F524" t="s">
+        <v>11</v>
+      </c>
+      <c r="G524" t="s">
+        <v>11</v>
+      </c>
+      <c r="H524" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
         <v>98</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B525" t="s">
         <v>49</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C525" t="s">
         <v>105</v>
       </c>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="D525" t="s">
+        <v>11</v>
+      </c>
+      <c r="E525" t="s">
+        <v>11</v>
+      </c>
+      <c r="F525" t="s">
+        <v>11</v>
+      </c>
+      <c r="G525" t="s">
+        <v>11</v>
+      </c>
+      <c r="H525" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
         <v>98</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B526" t="s">
         <v>49</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C526" t="s">
         <v>106</v>
       </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="D526" t="s">
+        <v>11</v>
+      </c>
+      <c r="E526" t="s">
+        <v>11</v>
+      </c>
+      <c r="F526" t="s">
+        <v>11</v>
+      </c>
+      <c r="G526" t="s">
+        <v>11</v>
+      </c>
+      <c r="H526" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
         <v>98</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B527" t="s">
         <v>49</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C527" t="s">
         <v>107</v>
       </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="D527" t="s">
+        <v>11</v>
+      </c>
+      <c r="E527" t="s">
+        <v>11</v>
+      </c>
+      <c r="F527" t="s">
+        <v>11</v>
+      </c>
+      <c r="G527" t="s">
+        <v>11</v>
+      </c>
+      <c r="H527" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
         <v>98</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B528" t="s">
         <v>49</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C528" t="s">
         <v>108</v>
       </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="D528" t="s">
+        <v>11</v>
+      </c>
+      <c r="E528" t="s">
+        <v>11</v>
+      </c>
+      <c r="F528" t="s">
+        <v>11</v>
+      </c>
+      <c r="G528" t="s">
+        <v>11</v>
+      </c>
+      <c r="H528" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
         <v>109</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B529" t="s">
         <v>32</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C529" t="s">
         <v>110</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D529" t="s">
         <v>111</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E529" t="s">
         <v>112</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F529" t="s">
         <v>113</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G529" t="s">
         <v>114</v>
       </c>
-      <c r="H31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="H529" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
         <v>109</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B530" t="s">
         <v>38</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C530" t="s">
         <v>115</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D530" t="s">
         <v>116</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E530" t="s">
         <v>117</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F530" t="s">
         <v>118</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G530" t="s">
         <v>114</v>
       </c>
-      <c r="H32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="H530" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
         <v>109</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B531" t="s">
         <v>49</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C531" t="s">
         <v>119</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D531" t="s">
         <v>120</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E531" t="s">
         <v>121</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F531" t="s">
         <v>122</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G531" t="s">
         <v>123</v>
       </c>
-      <c r="H33" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="H531" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
         <v>109</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B532" t="s">
         <v>49</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C532" t="s">
         <v>124</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D532" t="s">
         <v>125</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E532" t="s">
         <v>126</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F532" t="s">
         <v>127</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G532" t="s">
         <v>128</v>
       </c>
-      <c r="H34" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="H532" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
         <v>109</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B533" t="s">
         <v>49</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C533" t="s">
         <v>129</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D533" t="s">
         <v>130</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E533" t="s">
         <v>131</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F533" t="s">
         <v>132</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G533" t="s">
         <v>114</v>
       </c>
-      <c r="H35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="H533" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
         <v>133</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B534" t="s">
         <v>32</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C534" t="s">
         <v>134</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D534" t="s">
         <v>135</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E534" t="s">
         <v>136</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F534" t="s">
         <v>137</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G534" t="s">
         <v>138</v>
       </c>
-      <c r="H36" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="H534" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A535" t="s">
         <v>133</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B535" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C535" t="s">
         <v>139</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D535" t="s">
         <v>140</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E535" t="s">
         <v>141</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F535" t="s">
         <v>142</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G535" t="s">
         <v>143</v>
       </c>
-      <c r="H37" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="H535" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A536" t="s">
         <v>133</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B536" t="s">
         <v>38</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C536" t="s">
         <v>139</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D536" t="s">
         <v>144</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E536" t="s">
         <v>145</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F536" t="s">
         <v>146</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G536" t="s">
         <v>143</v>
       </c>
-      <c r="H38" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="H536" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A537" t="s">
         <v>133</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B537" t="s">
         <v>49</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C537" t="s">
         <v>147</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D537" t="s">
         <v>148</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E537" t="s">
         <v>149</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F537" t="s">
         <v>150</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G537" t="s">
         <v>151</v>
       </c>
-      <c r="H39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="H537" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
         <v>133</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B538" t="s">
         <v>49</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C538" t="s">
         <v>152</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D538" t="s">
         <v>153</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E538" t="s">
         <v>154</v>
       </c>
-      <c r="F40" t="s">
-        <v>11</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="F538" t="s">
+        <v>11</v>
+      </c>
+      <c r="G538" t="s">
         <v>155</v>
       </c>
-      <c r="H40" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="H538" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
         <v>133</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B539" t="s">
         <v>49</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C539" t="s">
         <v>156</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D539" t="s">
         <v>157</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E539" t="s">
         <v>158</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F539" t="s">
         <v>159</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G539" t="s">
         <v>138</v>
       </c>
-      <c r="H41" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="H539" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
         <v>133</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B540" t="s">
         <v>49</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C540" t="s">
         <v>160</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D540" t="s">
         <v>161</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E540" t="s">
         <v>162</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F540" t="s">
         <v>163</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G540" t="s">
         <v>164</v>
       </c>
-      <c r="H42" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="H540" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
         <v>133</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B541" t="s">
         <v>49</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C541" t="s">
         <v>165</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D541" t="s">
         <v>166</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E541" t="s">
         <v>167</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F541" t="s">
         <v>168</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G541" t="s">
         <v>169</v>
       </c>
-      <c r="H43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="H541" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
         <v>133</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B542" t="s">
         <v>49</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C542" t="s">
         <v>170</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D542" t="s">
         <v>171</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E542" t="s">
         <v>172</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F542" t="s">
         <v>173</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G542" t="s">
         <v>174</v>
       </c>
-      <c r="H44" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="H542" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
         <v>133</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B543" t="s">
         <v>49</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C543" t="s">
         <v>175</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D543" t="s">
         <v>176</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E543" t="s">
         <v>177</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F543" t="s">
         <v>178</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G543" t="s">
         <v>179</v>
       </c>
-      <c r="H45" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="H543" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
         <v>180</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B544" t="s">
         <v>32</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C544" t="s">
         <v>181</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D544" t="s">
         <v>182</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E544" t="s">
         <v>183</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F544" t="s">
         <v>184</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G544" t="s">
         <v>185</v>
       </c>
-      <c r="H46" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="H544" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
         <v>180</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B545" t="s">
         <v>38</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C545" t="s">
         <v>186</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D545" t="s">
         <v>187</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E545" t="s">
         <v>188</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F545" t="s">
         <v>189</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G545" t="s">
         <v>185</v>
       </c>
-      <c r="H47" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="H545" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
         <v>180</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B546" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C546" t="s">
         <v>190</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D546" t="s">
         <v>191</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E546" t="s">
         <v>192</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F546" t="s">
         <v>193</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G546" t="s">
         <v>194</v>
       </c>
-      <c r="H48" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="H546" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
         <v>180</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B547" t="s">
         <v>49</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C547" t="s">
         <v>195</v>
       </c>
-      <c r="D49" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" t="s">
-        <v>11</v>
-      </c>
-      <c r="G49" t="s">
-        <v>11</v>
-      </c>
-      <c r="H49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="D547" t="s">
+        <v>11</v>
+      </c>
+      <c r="E547" t="s">
+        <v>11</v>
+      </c>
+      <c r="F547" t="s">
+        <v>11</v>
+      </c>
+      <c r="G547" t="s">
+        <v>11</v>
+      </c>
+      <c r="H547" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
         <v>180</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B548" t="s">
         <v>49</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C548" t="s">
         <v>196</v>
       </c>
-      <c r="D50" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" t="s">
-        <v>11</v>
-      </c>
-      <c r="G50" t="s">
-        <v>11</v>
-      </c>
-      <c r="H50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="D548" t="s">
+        <v>11</v>
+      </c>
+      <c r="E548" t="s">
+        <v>11</v>
+      </c>
+      <c r="F548" t="s">
+        <v>11</v>
+      </c>
+      <c r="G548" t="s">
+        <v>11</v>
+      </c>
+      <c r="H548" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
         <v>180</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B549" t="s">
         <v>49</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C549" t="s">
         <v>197</v>
       </c>
-      <c r="D51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" t="s">
-        <v>11</v>
-      </c>
-      <c r="G51" t="s">
-        <v>11</v>
-      </c>
-      <c r="H51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="D549" t="s">
+        <v>11</v>
+      </c>
+      <c r="E549" t="s">
+        <v>11</v>
+      </c>
+      <c r="F549" t="s">
+        <v>11</v>
+      </c>
+      <c r="G549" t="s">
+        <v>11</v>
+      </c>
+      <c r="H549" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
         <v>198</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B550" t="s">
         <v>32</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C550" t="s">
         <v>199</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D550" t="s">
         <v>200</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E550" t="s">
         <v>201</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F550" t="s">
         <v>202</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G550" t="s">
         <v>203</v>
       </c>
-      <c r="H52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="H550" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
         <v>198</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B551" t="s">
         <v>38</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C551" t="s">
         <v>204</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D551" t="s">
         <v>205</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E551" t="s">
         <v>206</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F551" t="s">
         <v>207</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G551" t="s">
         <v>203</v>
       </c>
-      <c r="H53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="H551" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="552" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
         <v>198</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B552" t="s">
         <v>49</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C552" t="s">
         <v>208</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D552" t="s">
         <v>209</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E552" t="s">
         <v>210</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F552" t="s">
         <v>211</v>
       </c>
-      <c r="G54" t="s">
+      <c r="G552" t="s">
         <v>203</v>
       </c>
-      <c r="H54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="H552" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
         <v>198</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B553" t="s">
         <v>49</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C553" t="s">
         <v>212</v>
       </c>
-      <c r="D55" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" t="s">
-        <v>11</v>
-      </c>
-      <c r="G55" t="s">
-        <v>11</v>
-      </c>
-      <c r="H55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="D553" t="s">
+        <v>11</v>
+      </c>
+      <c r="E553" t="s">
+        <v>11</v>
+      </c>
+      <c r="F553" t="s">
+        <v>11</v>
+      </c>
+      <c r="G553" t="s">
+        <v>11</v>
+      </c>
+      <c r="H553" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
         <v>198</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B554" t="s">
         <v>49</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C554" t="s">
         <v>213</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D554" t="s">
         <v>214</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E554" t="s">
         <v>215</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F554" t="s">
         <v>216</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G554" t="s">
         <v>203</v>
       </c>
-      <c r="H56" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="H554" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
         <v>10</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B555" t="s">
         <v>49</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C555" t="s">
         <v>217</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D555" t="s">
         <v>17</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E555" t="s">
         <v>18</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F555" t="s">
         <v>19</v>
       </c>
-      <c r="G57" t="s">
+      <c r="G555" t="s">
         <v>16</v>
       </c>
-      <c r="H57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="H555" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
         <v>198</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B556" t="s">
         <v>49</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C556" t="s">
         <v>218</v>
       </c>
-      <c r="D58" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" t="s">
-        <v>11</v>
-      </c>
-      <c r="G58" t="s">
-        <v>11</v>
-      </c>
-      <c r="H58" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="D556" t="s">
+        <v>11</v>
+      </c>
+      <c r="E556" t="s">
+        <v>11</v>
+      </c>
+      <c r="F556" t="s">
+        <v>11</v>
+      </c>
+      <c r="G556" t="s">
+        <v>11</v>
+      </c>
+      <c r="H556" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
         <v>198</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B557" t="s">
         <v>49</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C557" t="s">
         <v>219</v>
       </c>
-      <c r="D59" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" t="s">
-        <v>11</v>
-      </c>
-      <c r="G59" t="s">
-        <v>11</v>
-      </c>
-      <c r="H59" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="D557" t="s">
+        <v>11</v>
+      </c>
+      <c r="E557" t="s">
+        <v>11</v>
+      </c>
+      <c r="F557" t="s">
+        <v>11</v>
+      </c>
+      <c r="G557" t="s">
+        <v>11</v>
+      </c>
+      <c r="H557" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
         <v>198</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B558" t="s">
         <v>49</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C558" t="s">
         <v>220</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D558" t="s">
         <v>221</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E558" t="s">
         <v>222</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F558" t="s">
         <v>223</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G558" t="s">
         <v>203</v>
       </c>
-      <c r="H60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="H558" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
         <v>224</v>
       </c>
-      <c r="B61" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="B559" t="s">
+        <v>11</v>
+      </c>
+      <c r="C559" t="s">
         <v>224</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D559" t="s">
         <v>225</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E559" t="s">
         <v>226</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F559" t="s">
         <v>227</v>
       </c>
-      <c r="G61" t="s">
-        <v>11</v>
-      </c>
-      <c r="H61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="G559" t="s">
+        <v>11</v>
+      </c>
+      <c r="H559" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
         <v>224</v>
       </c>
-      <c r="B62" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="B560" t="s">
+        <v>11</v>
+      </c>
+      <c r="C560" t="s">
         <v>224</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D560" t="s">
         <v>228</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E560" t="s">
         <v>229</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F560" t="s">
         <v>230</v>
       </c>
-      <c r="G62" t="s">
-        <v>11</v>
-      </c>
-      <c r="H62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="G560" t="s">
+        <v>11</v>
+      </c>
+      <c r="H560" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
         <v>224</v>
       </c>
-      <c r="B63" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="B561" t="s">
+        <v>11</v>
+      </c>
+      <c r="C561" t="s">
         <v>224</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D561" t="s">
         <v>231</v>
       </c>
-      <c r="E63" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" t="s">
-        <v>11</v>
-      </c>
-      <c r="G63" t="s">
-        <v>11</v>
-      </c>
-      <c r="H63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="E561" t="s">
+        <v>11</v>
+      </c>
+      <c r="F561" t="s">
+        <v>11</v>
+      </c>
+      <c r="G561" t="s">
+        <v>11</v>
+      </c>
+      <c r="H561" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
         <v>224</v>
       </c>
-      <c r="B64" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="B562" t="s">
+        <v>11</v>
+      </c>
+      <c r="C562" t="s">
         <v>224</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D562" t="s">
         <v>232</v>
       </c>
-      <c r="E64" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" t="s">
-        <v>11</v>
-      </c>
-      <c r="G64" t="s">
-        <v>11</v>
-      </c>
-      <c r="H64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="E562" t="s">
+        <v>11</v>
+      </c>
+      <c r="F562" t="s">
+        <v>11</v>
+      </c>
+      <c r="G562" t="s">
+        <v>11</v>
+      </c>
+      <c r="H562" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
         <v>31</v>
       </c>
-      <c r="B65" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="B563" t="s">
+        <v>11</v>
+      </c>
+      <c r="C563" t="s">
         <v>50</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D563" t="s">
         <v>233</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E563" t="s">
         <v>234</v>
       </c>
-      <c r="F65" t="s">
-        <v>11</v>
-      </c>
-      <c r="G65" t="s">
+      <c r="F563" t="s">
+        <v>11</v>
+      </c>
+      <c r="G563" t="s">
         <v>37</v>
       </c>
-      <c r="H65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="H563" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
         <v>31</v>
       </c>
-      <c r="B66" t="s">
-        <v>11</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="B564" t="s">
+        <v>11</v>
+      </c>
+      <c r="C564" t="s">
         <v>50</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D564" t="s">
         <v>235</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E564" t="s">
         <v>236</v>
       </c>
-      <c r="F66" t="s">
-        <v>11</v>
-      </c>
-      <c r="G66" t="s">
+      <c r="F564" t="s">
+        <v>11</v>
+      </c>
+      <c r="G564" t="s">
         <v>37</v>
       </c>
-      <c r="H66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="H564" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
         <v>31</v>
       </c>
-      <c r="B67" t="s">
-        <v>11</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="B565" t="s">
+        <v>11</v>
+      </c>
+      <c r="C565" t="s">
         <v>237</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D565" t="s">
         <v>238</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E565" t="s">
         <v>239</v>
       </c>
-      <c r="F67" t="s">
-        <v>11</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="F565" t="s">
+        <v>11</v>
+      </c>
+      <c r="G565" t="s">
         <v>37</v>
       </c>
-      <c r="H67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="H565" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
         <v>31</v>
       </c>
-      <c r="B68" t="s">
-        <v>11</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="B566" t="s">
+        <v>11</v>
+      </c>
+      <c r="C566" t="s">
         <v>237</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D566" t="s">
         <v>240</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E566" t="s">
         <v>241</v>
       </c>
-      <c r="F68" t="s">
-        <v>11</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="F566" t="s">
+        <v>11</v>
+      </c>
+      <c r="G566" t="s">
         <v>37</v>
       </c>
-      <c r="H68" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="H566" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
         <v>31</v>
       </c>
-      <c r="B69" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="B567" t="s">
+        <v>11</v>
+      </c>
+      <c r="C567" t="s">
         <v>242</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D567" t="s">
         <v>243</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E567" t="s">
         <v>244</v>
       </c>
-      <c r="F69" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69" t="s">
+      <c r="F567" t="s">
+        <v>11</v>
+      </c>
+      <c r="G567" t="s">
         <v>37</v>
       </c>
-      <c r="H69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="H567" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
         <v>31</v>
       </c>
-      <c r="B70" t="s">
-        <v>11</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="B568" t="s">
+        <v>11</v>
+      </c>
+      <c r="C568" t="s">
         <v>64</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D568" t="s">
         <v>245</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E568" t="s">
         <v>246</v>
       </c>
-      <c r="F70" t="s">
-        <v>11</v>
-      </c>
-      <c r="G70" t="s">
+      <c r="F568" t="s">
+        <v>11</v>
+      </c>
+      <c r="G568" t="s">
         <v>67</v>
       </c>
-      <c r="H70" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="H568" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
         <v>31</v>
       </c>
-      <c r="B71" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="B569" t="s">
+        <v>11</v>
+      </c>
+      <c r="C569" t="s">
         <v>64</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D569" t="s">
         <v>247</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E569" t="s">
         <v>248</v>
       </c>
-      <c r="F71" t="s">
-        <v>11</v>
-      </c>
-      <c r="G71" t="s">
+      <c r="F569" t="s">
+        <v>11</v>
+      </c>
+      <c r="G569" t="s">
         <v>67</v>
       </c>
-      <c r="H71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="H569" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
         <v>98</v>
       </c>
-      <c r="B72" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="B570" t="s">
+        <v>11</v>
+      </c>
+      <c r="C570" t="s">
         <v>106</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D570" t="s">
         <v>249</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E570" t="s">
         <v>250</v>
       </c>
-      <c r="F72" t="s">
-        <v>11</v>
-      </c>
-      <c r="G72" t="s">
+      <c r="F570" t="s">
+        <v>11</v>
+      </c>
+      <c r="G570" t="s">
         <v>103</v>
       </c>
-      <c r="H72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="H570" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
         <v>98</v>
       </c>
-      <c r="B73" t="s">
-        <v>11</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="B571" t="s">
+        <v>11</v>
+      </c>
+      <c r="C571" t="s">
         <v>251</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D571" t="s">
         <v>252</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E571" t="s">
         <v>253</v>
       </c>
-      <c r="F73" t="s">
-        <v>11</v>
-      </c>
-      <c r="G73" t="s">
+      <c r="F571" t="s">
+        <v>11</v>
+      </c>
+      <c r="G571" t="s">
         <v>103</v>
       </c>
-      <c r="H73" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="H571" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
         <v>198</v>
       </c>
-      <c r="B74" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="B572" t="s">
+        <v>11</v>
+      </c>
+      <c r="C572" t="s">
         <v>212</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D572" t="s">
         <v>254</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E572" t="s">
         <v>255</v>
       </c>
-      <c r="F74" t="s">
-        <v>11</v>
-      </c>
-      <c r="G74" t="s">
+      <c r="F572" t="s">
+        <v>11</v>
+      </c>
+      <c r="G572" t="s">
         <v>203</v>
       </c>
-      <c r="H74" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="H572" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
         <v>224</v>
       </c>
-      <c r="B75" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="B573" t="s">
+        <v>11</v>
+      </c>
+      <c r="C573" t="s">
         <v>256</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D573" t="s">
         <v>257</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E573" t="s">
         <v>234</v>
       </c>
-      <c r="F75" t="s">
-        <v>11</v>
-      </c>
-      <c r="G75" t="s">
+      <c r="F573" t="s">
+        <v>11</v>
+      </c>
+      <c r="G573" t="s">
         <v>258</v>
       </c>
-      <c r="H75" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="H573" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
         <v>20</v>
       </c>
-      <c r="B76" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" t="s">
+      <c r="B574" t="s">
+        <v>11</v>
+      </c>
+      <c r="C574" t="s">
         <v>21</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D574" t="s">
         <v>259</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E574" t="s">
         <v>260</v>
       </c>
-      <c r="F76" t="s">
-        <v>11</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="F574" t="s">
+        <v>11</v>
+      </c>
+      <c r="G574" t="s">
         <v>261</v>
       </c>
-      <c r="H76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="H574" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A575" t="s">
         <v>20</v>
       </c>
-      <c r="B77" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="B575" t="s">
+        <v>11</v>
+      </c>
+      <c r="C575" t="s">
         <v>26</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D575" t="s">
         <v>262</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E575" t="s">
         <v>263</v>
       </c>
-      <c r="F77" t="s">
-        <v>11</v>
-      </c>
-      <c r="G77" t="s">
+      <c r="F575" t="s">
+        <v>11</v>
+      </c>
+      <c r="G575" t="s">
         <v>264</v>
       </c>
-      <c r="H77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="H575" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A576" t="s">
         <v>31</v>
       </c>
-      <c r="B78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="B576" t="s">
+        <v>11</v>
+      </c>
+      <c r="C576" t="s">
         <v>39</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D576" t="s">
         <v>265</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E576" t="s">
         <v>266</v>
       </c>
-      <c r="F78" t="s">
-        <v>11</v>
-      </c>
-      <c r="G78" t="s">
+      <c r="F576" t="s">
+        <v>11</v>
+      </c>
+      <c r="G576" t="s">
         <v>267</v>
       </c>
-      <c r="H78" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="H576" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A577" t="s">
         <v>68</v>
       </c>
-      <c r="B79" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="B577" t="s">
+        <v>11</v>
+      </c>
+      <c r="C577" t="s">
         <v>74</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D577" t="s">
         <v>268</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E577" t="s">
         <v>269</v>
       </c>
-      <c r="F79" t="s">
-        <v>11</v>
-      </c>
-      <c r="G79" t="s">
+      <c r="F577" t="s">
+        <v>11</v>
+      </c>
+      <c r="G577" t="s">
         <v>270</v>
       </c>
-      <c r="H79" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="H577" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
         <v>68</v>
       </c>
-      <c r="B80" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="B578" t="s">
+        <v>11</v>
+      </c>
+      <c r="C578" t="s">
         <v>271</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D578" t="s">
         <v>272</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E578" t="s">
         <v>273</v>
       </c>
-      <c r="F80" t="s">
-        <v>11</v>
-      </c>
-      <c r="G80" t="s">
+      <c r="F578" t="s">
+        <v>11</v>
+      </c>
+      <c r="G578" t="s">
         <v>274</v>
       </c>
-      <c r="H80" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="H578" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
         <v>133</v>
       </c>
-      <c r="B81" t="s">
-        <v>11</v>
-      </c>
-      <c r="C81" t="s">
+      <c r="B579" t="s">
+        <v>11</v>
+      </c>
+      <c r="C579" t="s">
         <v>139</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D579" t="s">
         <v>275</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E579" t="s">
         <v>276</v>
       </c>
-      <c r="F81" t="s">
-        <v>11</v>
-      </c>
-      <c r="G81" t="s">
+      <c r="F579" t="s">
+        <v>11</v>
+      </c>
+      <c r="G579" t="s">
         <v>277</v>
       </c>
-      <c r="H81" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="H579" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A580" t="s">
         <v>68</v>
       </c>
-      <c r="B82" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="B580" t="s">
+        <v>11</v>
+      </c>
+      <c r="C580" t="s">
         <v>278</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D580" t="s">
         <v>279</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E580" t="s">
         <v>280</v>
       </c>
-      <c r="F82" t="s">
-        <v>11</v>
-      </c>
-      <c r="G82" t="s">
+      <c r="F580" t="s">
+        <v>11</v>
+      </c>
+      <c r="G580" t="s">
         <v>281</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H580" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <dataValidations count="4">
+    <dataValidation showInputMessage="1" promptTitle="姓名　格式" prompt="一格只准一個人。兩個人要開兩行 —— 2026 就係有一格寫咗兩個人，搞到 55 行變 54 人。  ✓ 可以：陳大文、區永樑先生 ✗ 唔好：陳大文、李小明、陳大文/李小明、陳大文 (待定)" sqref="D10:D500"/>
+    <dataValidation showInputMessage="1" promptTitle="姓名　格式" prompt="一格只准一個人。兩個人要開兩行 —— 2026 就係有一格寫咗兩個人，搞到 55 行變 54 人。  ✓ 可以：陳大文、區永樑先生 ✗ 唔好：陳大文、李小明、陳大文/李小明、陳大文 (待定)" sqref="D3:D500"/>
+    <dataValidation showInputMessage="1" promptTitle="電話　格式" prompt="只准填 8 位數字。唔好加 +852、空格、斜線或者「／」。  ✓ 可以：92157472 ✗ 唔好：+852 9215 7472、9215 7472、92157472/98765432（兩個號碼）、待定" sqref="E10:E500"/>
+    <dataValidation showInputMessage="1" promptTitle="電話　格式" prompt="只准填 8 位數字。唔好加 +852、空格、斜線或者「／」。  ✓ 可以：92157472 ✗ 唔好：+852 9215 7472、9215 7472、92157472/98765432（兩個號碼）、待定" sqref="E3:E500"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
@@ -3815,18 +4325,18 @@
         <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E16" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
@@ -3835,7 +4345,7 @@
         <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>312</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
         <v>14</v>
